--- a/results/ate_iptw_cox_standard_IPTW_Cox_Standard_retention.xlsx
+++ b/results/ate_iptw_cox_standard_IPTW_Cox_Standard_retention.xlsx
@@ -582,7 +582,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.22</v>
+        <v>0.336</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.068</v>
+        <v>0.028</v>
       </c>
       <c r="E6" t="n">
-        <v>0.152</v>
+        <v>0.308</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -609,7 +609,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -618,13 +618,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.402</v>
+        <v>-0.22</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.042</v>
+        <v>-0.068</v>
       </c>
       <c r="E7" t="n">
-        <v>0.36</v>
+        <v>0.152</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -636,7 +636,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.075</v>
+        <v>0.006</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.004</v>
+        <v>0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.028</v>
+        <v>0.024</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04100000000000001</v>
+        <v>0.015</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -690,7 +690,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="E10" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.039</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.024</v>
+        <v>0.001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.015</v>
+        <v>-0.001</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -771,7 +771,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -780,16 +780,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.027</v>
+        <v>0.359</v>
       </c>
       <c r="D13" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="E13" t="n">
-        <v>0.019</v>
+        <v>0.347</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -798,7 +798,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.336</v>
+        <v>-0.018</v>
       </c>
       <c r="D14" t="n">
-        <v>0.028</v>
+        <v>-0.004</v>
       </c>
       <c r="E14" t="n">
-        <v>0.308</v>
+        <v>0.014</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -825,7 +825,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.026</v>
+        <v>0.028</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.005</v>
+        <v>0.006</v>
       </c>
       <c r="E15" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -852,7 +852,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.186</v>
+        <v>-0.152</v>
       </c>
       <c r="D16" t="n">
         <v>0.023</v>
       </c>
       <c r="E16" t="n">
-        <v>0.163</v>
+        <v>0.129</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -879,7 +879,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.003</v>
       </c>
       <c r="D17" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="E17" t="n">
-        <v>0.08199999999999999</v>
+        <v>0</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -906,7 +906,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.081</v>
+        <v>-0.026</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.031</v>
+        <v>-0.005</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05</v>
+        <v>0.021</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -933,7 +933,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -942,16 +942,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.152</v>
+        <v>0.013</v>
       </c>
       <c r="D19" t="n">
-        <v>0.023</v>
+        <v>0.013</v>
       </c>
       <c r="E19" t="n">
-        <v>0.129</v>
+        <v>0</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -960,7 +960,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.013</v>
+        <v>-0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -987,7 +987,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.006</v>
+        <v>0.054</v>
       </c>
       <c r="D21" t="n">
-        <v>0.002</v>
+        <v>0.015</v>
       </c>
       <c r="E21" t="n">
-        <v>0.004</v>
+        <v>0.039</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1041,7 +1041,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>0.001</v>
+        <v>-0.028</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.001</v>
+        <v>0.04100000000000001</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1068,7 +1068,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.054</v>
+        <v>0.081</v>
       </c>
       <c r="D24" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="E24" t="n">
-        <v>0.039</v>
+        <v>0.07100000000000001</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1095,7 +1095,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.005</v>
+        <v>-0.024</v>
       </c>
       <c r="E25" t="n">
-        <v>0.003999999999999999</v>
+        <v>-0.024</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1122,7 +1122,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0</v>
+        <v>-0.075</v>
       </c>
       <c r="D26" t="n">
-        <v>0.014</v>
+        <v>-0.004</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.014</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1149,7 +1149,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.018</v>
+        <v>0.061</v>
       </c>
       <c r="D27" t="n">
         <v>-0.004</v>
       </c>
       <c r="E27" t="n">
-        <v>0.014</v>
+        <v>0.057</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1176,7 +1176,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1185,16 +1185,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.359</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="E28" t="n">
-        <v>0.347</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1203,7 +1203,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.024</v>
+        <v>0.005</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.024</v>
+        <v>0.003999999999999999</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1230,7 +1230,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1239,16 +1239,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.061</v>
+        <v>0.186</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.004</v>
+        <v>0.023</v>
       </c>
       <c r="E30" t="n">
-        <v>0.057</v>
+        <v>0.163</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1257,7 +1257,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.003</v>
+        <v>-0.402</v>
       </c>
       <c r="D31" t="n">
-        <v>0.003</v>
+        <v>-0.042</v>
       </c>
       <c r="E31" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F31" t="b">
         <v>0</v>
-      </c>
-      <c r="F31" t="b">
-        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1284,7 +1284,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.081</v>
+        <v>-0.081</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01</v>
+        <v>-0.031</v>
       </c>
       <c r="E32" t="n">
-        <v>0.07100000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1370,16 +1370,16 @@
         <v>0.995002785613916</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1488435642969906</v>
+        <v>0.1488435642969905</v>
       </c>
       <c r="E2" t="n">
-        <v>1.761326673294263</v>
+        <v>1.761326673294262</v>
       </c>
       <c r="F2" t="n">
         <v>1.137318832200253</v>
       </c>
       <c r="G2" t="n">
-        <v>1.759851730165227</v>
+        <v>1.759851730165226</v>
       </c>
     </row>
   </sheetData>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.565853031636363</v>
+        <v>-2.565853031636366</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4408682502540033</v>
+        <v>0.4408682502539966</v>
       </c>
       <c r="D2" t="n">
-        <v>5.884777503710434e-09</v>
+        <v>5.884777503707101e-09</v>
       </c>
     </row>
     <row r="3">
@@ -1609,13 +1609,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02444271798652553</v>
+        <v>0.02444271798652562</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1018579889442993</v>
+        <v>0.1018579889442992</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8103546067770735</v>
+        <v>0.8103546067770725</v>
       </c>
     </row>
     <row r="4">
@@ -1628,10 +1628,10 @@
         <v>0.2756487250199113</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2218639632557894</v>
+        <v>0.2218639632557895</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2140808095272578</v>
+        <v>0.2140808095272581</v>
       </c>
     </row>
     <row r="5">
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1791283976706458</v>
+        <v>-0.1791283976706456</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2049919256074304</v>
+        <v>0.2049919256074302</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3822100343131284</v>
+        <v>0.3822100343131282</v>
       </c>
     </row>
     <row r="7">
@@ -1676,10 +1676,10 @@
         <v>0.1904728809612527</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1830828687785755</v>
+        <v>0.1830828687785754</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2981706802576989</v>
+        <v>0.2981706802576984</v>
       </c>
     </row>
     <row r="8">
@@ -1689,13 +1689,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02585714966741427</v>
+        <v>0.02585714966741434</v>
       </c>
       <c r="C8" t="n">
-        <v>0.193137731954017</v>
+        <v>0.1931377319540168</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8934979973795412</v>
+        <v>0.8934979973795407</v>
       </c>
     </row>
     <row r="9">
@@ -1708,10 +1708,10 @@
         <v>1.078492441903574</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1625051351014596</v>
+        <v>0.1625051351014593</v>
       </c>
       <c r="D9" t="n">
-        <v>3.208557236657116e-11</v>
+        <v>3.208557236656847e-11</v>
       </c>
     </row>
     <row r="10">
@@ -1721,13 +1721,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1453095305392676</v>
+        <v>0.1453095305392677</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2667530368267074</v>
+        <v>0.266753036826706</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5859362662578804</v>
+        <v>0.5859362662578781</v>
       </c>
     </row>
     <row r="11">
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2258952284551361</v>
+        <v>0.2258952284551363</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2567372932128593</v>
+        <v>0.2567372932128584</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3789301892340646</v>
+        <v>0.3789301892340624</v>
       </c>
     </row>
     <row r="12">
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2238722198593794</v>
+        <v>-0.2238722198593791</v>
       </c>
       <c r="C12" t="n">
-        <v>0.292143100926569</v>
+        <v>0.2921431009265691</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4434917877305503</v>
+        <v>0.4434917877305512</v>
       </c>
     </row>
     <row r="13">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2014123494531393</v>
+        <v>0.2014123494531396</v>
       </c>
       <c r="C13" t="n">
         <v>0.2595890034850308</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4378143071063252</v>
+        <v>0.4378143071063244</v>
       </c>
     </row>
     <row r="14">
@@ -1785,13 +1785,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2380082564065342</v>
+        <v>0.2380082564065347</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2619585733909516</v>
+        <v>0.2619585733909518</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3635760286774822</v>
+        <v>0.3635760286774815</v>
       </c>
     </row>
     <row r="15">
@@ -1801,13 +1801,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2909332948528219</v>
+        <v>0.2909332948528223</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2546715666353523</v>
+        <v>0.2546715666353525</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2532935059734772</v>
+        <v>0.2532935059734768</v>
       </c>
     </row>
     <row r="16">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1481947915129309</v>
+        <v>0.1481947915129312</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2510856640294913</v>
+        <v>0.2510856640294915</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5550458059667093</v>
+        <v>0.5550458059667087</v>
       </c>
     </row>
     <row r="17">
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1147419350152479</v>
+        <v>0.1147419350152481</v>
       </c>
       <c r="C17" t="n">
-        <v>0.263465466196073</v>
+        <v>0.2634654661960734</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6631920346004131</v>
+        <v>0.663192034600413</v>
       </c>
     </row>
     <row r="18">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3810056013756244</v>
+        <v>0.3810056013756247</v>
       </c>
       <c r="C18" t="n">
         <v>0.2516542446197348</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1300247560438155</v>
+        <v>0.1300247560438152</v>
       </c>
     </row>
     <row r="19">
@@ -1865,13 +1865,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0757720720296971</v>
+        <v>0.07577207202969742</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2639063601658803</v>
+        <v>0.2639063601658794</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7740225338446061</v>
+        <v>0.7740225338446043</v>
       </c>
     </row>
     <row r="20">
@@ -1881,13 +1881,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1514048112017342</v>
+        <v>0.1514048112017345</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2657254019096257</v>
+        <v>0.265725401909625</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5688274538815613</v>
+        <v>0.5688274538815593</v>
       </c>
     </row>
     <row r="21">
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.200249686815133</v>
+        <v>0.2002496868151333</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2549038121769299</v>
+        <v>0.25490381217693</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4321081823507374</v>
+        <v>0.432108182350737</v>
       </c>
     </row>
     <row r="22">
@@ -1913,13 +1913,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.02074852137919077</v>
+        <v>-0.02074852137919054</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2743224548273926</v>
+        <v>0.2743224548273922</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9397090769219659</v>
+        <v>0.9397090769219666</v>
       </c>
     </row>
     <row r="23">
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1368482394108763</v>
+        <v>-0.136848239410876</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2792240338270784</v>
+        <v>0.2792240338270775</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6240617685694629</v>
+        <v>0.6240617685694627</v>
       </c>
     </row>
     <row r="24">
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8213945685289852</v>
+        <v>0.8213945685289854</v>
       </c>
       <c r="C24" t="n">
         <v>0.1484879382665879</v>
       </c>
       <c r="D24" t="n">
-        <v>3.170952111067041e-08</v>
+        <v>3.170952111067024e-08</v>
       </c>
     </row>
     <row r="25">
@@ -1961,13 +1961,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.6343958972733734</v>
+        <v>-0.6343958972733733</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1108031950759137</v>
+        <v>0.1108031950759136</v>
       </c>
       <c r="D25" t="n">
-        <v>1.031722996890053e-08</v>
+        <v>1.031722996890038e-08</v>
       </c>
     </row>
     <row r="26">
@@ -1980,10 +1980,10 @@
         <v>-0.1361722920117852</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1456889183422692</v>
+        <v>0.1456889183422691</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3499540372786678</v>
+        <v>0.3499540372786675</v>
       </c>
     </row>
     <row r="27">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0721458957078063</v>
+        <v>-0.07214589570780619</v>
       </c>
       <c r="C27" t="n">
         <v>0.1495438291756702</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6294935505006776</v>
+        <v>0.6294935505006782</v>
       </c>
     </row>
     <row r="28">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.08070056949942792</v>
+        <v>-0.08070056949942785</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1455600496406538</v>
+        <v>0.1455600496406539</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5792953583346232</v>
+        <v>0.5792953583346238</v>
       </c>
     </row>
     <row r="29">
@@ -2025,13 +2025,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.267089354671909</v>
+        <v>-0.2670893546719089</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1498065967867205</v>
+        <v>0.1498065967867206</v>
       </c>
       <c r="D29" t="n">
-        <v>0.07460348161737988</v>
+        <v>0.07460348161738017</v>
       </c>
     </row>
     <row r="30">
@@ -2041,13 +2041,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.01036511117109712</v>
+        <v>-0.01036511117109708</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00765393380726719</v>
+        <v>0.007653933807267039</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1756661613316916</v>
+        <v>0.1756661613316849</v>
       </c>
     </row>
     <row r="31">
@@ -2057,45 +2057,45 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01050692349724877</v>
+        <v>0.01050692349724878</v>
       </c>
       <c r="C31" t="n">
-        <v>0.006731266320498103</v>
+        <v>0.006731266320498094</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1185441957481896</v>
+        <v>0.118544195748189</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.002276675805551763</v>
+        <v>0.01407014842112891</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007061859833278312</v>
+        <v>0.02184983277761078</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7471569571762012</v>
+        <v>0.5196093827488846</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01407014842112883</v>
+        <v>0.002276675805551766</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02184983277761042</v>
+        <v>0.007061859833278298</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5196093827488801</v>
+        <v>0.7471569571762005</v>
       </c>
     </row>
   </sheetData>
@@ -2168,13 +2168,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9076439572638424</v>
+        <v>0.9076439572638432</v>
       </c>
       <c r="D3" t="n">
         <v>0.8579106117563428</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04973334550749964</v>
+        <v>0.04973334550750041</v>
       </c>
     </row>
     <row r="4">
@@ -2187,13 +2187,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8958640717713845</v>
+        <v>0.8958640717713853</v>
       </c>
       <c r="D4" t="n">
         <v>0.8263333274535157</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06953074431786876</v>
+        <v>0.06953074431786954</v>
       </c>
     </row>
     <row r="5">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8710411710941851</v>
+        <v>0.8710411710941867</v>
       </c>
       <c r="D5" t="n">
         <v>0.794717184639996</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07632398645418914</v>
+        <v>0.0763239864541907</v>
       </c>
     </row>
   </sheetData>
@@ -2253,10 +2253,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.443505627120429</v>
+        <v>3.443505627120432</v>
       </c>
       <c r="B2" t="n">
-        <v>0.06350082160297775</v>
+        <v>0.06350082160297774</v>
       </c>
       <c r="C2" t="n">
         <v>3.977080931513962</v>
@@ -2265,55 +2265,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5903149678536233</v>
+        <v>0.5903149678536211</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4422973484463524</v>
+        <v>0.4422973484463532</v>
       </c>
       <c r="C3" t="n">
-        <v>1.176911501519809</v>
+        <v>1.176911501519807</v>
       </c>
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.6457416250634045</v>
+        <v>0.6457416250634048</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4216392867904264</v>
+        <v>0.4216392867904263</v>
       </c>
       <c r="C4" t="n">
-        <v>1.245918796657312</v>
+        <v>1.245918796657313</v>
       </c>
       <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.1158610022023808</v>
+        <v>0.1158610022023816</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7335676596604723</v>
+        <v>0.7335676596604714</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4469980577481745</v>
+        <v>0.4469980577481762</v>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.1658506004757236</v>
+        <v>0.1658506004757251</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6838261508744685</v>
+        <v>0.6838261508744673</v>
       </c>
       <c r="C6" t="n">
-        <v>0.548298499528296</v>
+        <v>0.5482984995282986</v>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.05554968572144039</v>
+        <v>0.0555496857214403</v>
       </c>
       <c r="B7" t="n">
         <v>0.8136733789568205</v>
@@ -2325,121 +2325,121 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.342656090985949</v>
+        <v>2.342656090985952</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1258747664385371</v>
+        <v>0.1258747664385362</v>
       </c>
       <c r="C8" t="n">
-        <v>2.989938993583024</v>
+        <v>2.989938993583034</v>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.4191648223707299</v>
+        <v>0.4191648223707315</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5173540760818469</v>
+        <v>0.517354076081846</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9507760987492871</v>
+        <v>0.9507760987492896</v>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2.563087620801928</v>
+        <v>2.56308762080192</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1093847620548841</v>
+        <v>0.109384762054885</v>
       </c>
       <c r="C10" t="n">
-        <v>3.192516318722262</v>
+        <v>3.192516318722249</v>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.01850173438861382</v>
+        <v>0.01850173438861422</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8918046158754556</v>
+        <v>0.8918046158754545</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1652004279969318</v>
+        <v>0.1652004279969336</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.7148191238207375</v>
+        <v>0.7148191238207384</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3978486067889273</v>
+        <v>0.397848606788927</v>
       </c>
       <c r="C12" t="n">
-        <v>1.329708548003163</v>
+        <v>1.329708548003164</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0486793493620209</v>
+        <v>0.04867934936202147</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8253774474283422</v>
+        <v>0.8253774474283412</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2768740761302493</v>
+        <v>0.276874076130251</v>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.1821552994077164</v>
+        <v>0.1821552994077157</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6695275158805051</v>
+        <v>0.6695275158805057</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5787847470172153</v>
+        <v>0.5787847470172138</v>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.299353244474762</v>
+        <v>0.2993532444747626</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5842881627155669</v>
+        <v>0.5842881627155665</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7752480333376613</v>
+        <v>0.7752480333376625</v>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.04913171654298543</v>
+        <v>0.04913171654298526</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8245810980309498</v>
+        <v>0.82458109803095</v>
       </c>
       <c r="C16" t="n">
-        <v>0.278266704349674</v>
+        <v>0.2782667043496737</v>
       </c>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.184202881563921</v>
+        <v>1.184202881563925</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2765020303717795</v>
+        <v>0.2765020303717787</v>
       </c>
       <c r="C17" t="n">
-        <v>1.854638020588166</v>
+        <v>1.85463802058817</v>
       </c>
       <c r="D17" t="inlineStr"/>
     </row>
@@ -2457,175 +2457,175 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2.804172748136155</v>
+        <v>2.804172748136175</v>
       </c>
       <c r="B19" t="n">
-        <v>0.09401932927339254</v>
+        <v>0.0940193292733911</v>
       </c>
       <c r="C19" t="n">
-        <v>3.41089880128096</v>
+        <v>3.410898801280982</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.009052018172400804</v>
+        <v>0.009052018172401151</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9242019630174045</v>
+        <v>0.9242019630174031</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1137199410759825</v>
+        <v>0.1137199410759848</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.861354950227986</v>
+        <v>0.8613549502279868</v>
       </c>
       <c r="B21" t="n">
-        <v>0.3533597960230549</v>
+        <v>0.3533597960230548</v>
       </c>
       <c r="C21" t="n">
-        <v>1.500790190192142</v>
+        <v>1.500790190192143</v>
       </c>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.3637986136795437</v>
+        <v>0.3637986136795444</v>
       </c>
       <c r="B22" t="n">
-        <v>0.5464041140521185</v>
+        <v>0.5464041140521181</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8719597487040061</v>
+        <v>0.8719597487040072</v>
       </c>
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1.530686883471327</v>
+        <v>1.530686883471331</v>
       </c>
       <c r="B23" t="n">
-        <v>0.2160093850510959</v>
+        <v>0.2160093850510954</v>
       </c>
       <c r="C23" t="n">
-        <v>2.210834099755395</v>
+        <v>2.210834099755398</v>
       </c>
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.0162096305996066</v>
+        <v>0.01620963059960664</v>
       </c>
       <c r="B24" t="n">
-        <v>0.8986894681032694</v>
+        <v>0.8986894681032693</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1541053998591764</v>
+        <v>0.1541053998591765</v>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2.275397032810749</v>
+        <v>2.275397032810745</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1314414603749735</v>
+        <v>0.1314414603749755</v>
       </c>
       <c r="C25" t="n">
-        <v>2.927507680393403</v>
+        <v>2.927507680393381</v>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.06770591936065655</v>
+        <v>0.0677059193606587</v>
       </c>
       <c r="B26" t="n">
-        <v>0.7947067187302206</v>
+        <v>0.7947067187302173</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3315055533556185</v>
+        <v>0.3315055533556245</v>
       </c>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.1600402696707897</v>
+        <v>0.1600402696707896</v>
       </c>
       <c r="B27" t="n">
-        <v>0.6891194441918254</v>
+        <v>0.6891194441918256</v>
       </c>
       <c r="C27" t="n">
-        <v>0.537174029797839</v>
+        <v>0.5371740297978385</v>
       </c>
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5.661975765712013</v>
+        <v>5.661975765712</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0173365827060885</v>
+        <v>0.0173365827060886</v>
       </c>
       <c r="C28" t="n">
-        <v>5.850036639476</v>
+        <v>5.850036639475991</v>
       </c>
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.5185416276853745</v>
+        <v>0.5185416276853725</v>
       </c>
       <c r="B29" t="n">
-        <v>0.4714644459190886</v>
+        <v>0.4714644459190896</v>
       </c>
       <c r="C29" t="n">
-        <v>1.084779116415932</v>
+        <v>1.084779116415929</v>
       </c>
       <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.612191031299769</v>
+        <v>0.6121910312997699</v>
       </c>
       <c r="B30" t="n">
-        <v>0.4339640388345912</v>
+        <v>0.4339640388345909</v>
       </c>
       <c r="C30" t="n">
-        <v>1.204352598633607</v>
+        <v>1.204352598633608</v>
       </c>
       <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.4311172894155759</v>
+        <v>0.4311172894155737</v>
       </c>
       <c r="B31" t="n">
-        <v>0.5114412200502627</v>
+        <v>0.5114412200502637</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9673596543594259</v>
+        <v>0.9673596543594232</v>
       </c>
       <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.7749116540198877</v>
+        <v>0.7749116540198883</v>
       </c>
       <c r="B32" t="n">
-        <v>0.3787018686058172</v>
+        <v>0.3787018686058168</v>
       </c>
       <c r="C32" t="n">
-        <v>1.400865555044235</v>
+        <v>1.400865555044237</v>
       </c>
       <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2.228476646075273</v>
+        <v>2.228476646075275</v>
       </c>
       <c r="B33" t="n">
         <v>0.1354873718065581</v>

--- a/results/ate_iptw_cox_standard_IPTW_Cox_Standard_retention.xlsx
+++ b/results/ate_iptw_cox_standard_IPTW_Cox_Standard_retention.xlsx
@@ -582,7 +582,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.336</v>
+        <v>0.006</v>
       </c>
       <c r="D6" t="n">
-        <v>0.028</v>
+        <v>0.002</v>
       </c>
       <c r="E6" t="n">
-        <v>0.308</v>
+        <v>0.004</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -609,7 +609,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.22</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.068</v>
+        <v>0.006</v>
       </c>
       <c r="E7" t="n">
-        <v>0.152</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -636,7 +636,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.006</v>
+        <v>0.054</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002</v>
+        <v>0.015</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004</v>
+        <v>0.039</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.039</v>
+        <v>0.003</v>
       </c>
       <c r="D9" t="n">
-        <v>0.024</v>
+        <v>-0.013</v>
       </c>
       <c r="E9" t="n">
-        <v>0.015</v>
+        <v>-0.009999999999999998</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0.359</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001</v>
+        <v>0.012</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.001</v>
+        <v>0.347</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -744,7 +744,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.005</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -771,7 +771,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -780,16 +780,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.359</v>
+        <v>0.039</v>
       </c>
       <c r="D13" t="n">
-        <v>0.012</v>
+        <v>0.024</v>
       </c>
       <c r="E13" t="n">
-        <v>0.347</v>
+        <v>0.015</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -798,7 +798,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.018</v>
+        <v>-0.152</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.004</v>
+        <v>0.023</v>
       </c>
       <c r="E14" t="n">
-        <v>0.014</v>
+        <v>0.129</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -825,7 +825,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.028</v>
+        <v>0.061</v>
       </c>
       <c r="D15" t="n">
-        <v>0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="E15" t="n">
-        <v>0.022</v>
+        <v>0.057</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -852,7 +852,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.152</v>
+        <v>-0.003</v>
       </c>
       <c r="D16" t="n">
-        <v>0.023</v>
+        <v>0.003</v>
       </c>
       <c r="E16" t="n">
-        <v>0.129</v>
+        <v>0</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -879,7 +879,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.003</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.003999999999999999</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -906,7 +906,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.026</v>
+        <v>0.336</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.005</v>
+        <v>0.028</v>
       </c>
       <c r="E18" t="n">
-        <v>0.021</v>
+        <v>0.308</v>
       </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -933,7 +933,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.013</v>
+        <v>-0.018</v>
       </c>
       <c r="D19" t="n">
-        <v>0.013</v>
+        <v>-0.004</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -960,7 +960,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.014</v>
+        <v>-0.028</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.014</v>
+        <v>0.04100000000000001</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -987,7 +987,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.054</v>
+        <v>0.186</v>
       </c>
       <c r="D21" t="n">
-        <v>0.015</v>
+        <v>0.023</v>
       </c>
       <c r="E21" t="n">
-        <v>0.039</v>
+        <v>0.163</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1014,7 +1014,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1023,16 +1023,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.003</v>
+        <v>-0.22</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.013</v>
+        <v>-0.068</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.009999999999999998</v>
+        <v>0.152</v>
       </c>
       <c r="F22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1041,7 +1041,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.028</v>
+        <v>0.005</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04100000000000001</v>
+        <v>0</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1068,7 +1068,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.081</v>
+        <v>-0.075</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07100000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1095,7 +1095,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1107,10 +1107,10 @@
         <v>-0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.024</v>
+        <v>0.001</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.024</v>
+        <v>-0.001</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1122,7 +1122,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.075</v>
+        <v>0.028</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.022</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1149,7 +1149,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.061</v>
+        <v>0.081</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.004</v>
+        <v>0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>0.057</v>
+        <v>0.07100000000000001</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1176,7 +1176,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.026</v>
       </c>
       <c r="D28" t="n">
-        <v>0.006</v>
+        <v>-0.005</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08199999999999999</v>
+        <v>0.021</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1203,7 +1203,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1212,16 +1212,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.402</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005</v>
+        <v>-0.042</v>
       </c>
       <c r="E29" t="n">
-        <v>0.003999999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="F29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1230,7 +1230,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1239,16 +1239,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.186</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.023</v>
+        <v>-0.024</v>
       </c>
       <c r="E30" t="n">
-        <v>0.163</v>
+        <v>-0.024</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1257,7 +1257,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.402</v>
+        <v>0.013</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.042</v>
+        <v>0.013</v>
       </c>
       <c r="E31" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.565853031636366</v>
+        <v>-2.565853031636364</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4408682502539966</v>
+        <v>0.4408682502540031</v>
       </c>
       <c r="D2" t="n">
-        <v>5.884777503707101e-09</v>
+        <v>5.88477750371024e-09</v>
       </c>
     </row>
     <row r="3">
@@ -1609,13 +1609,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02444271798652562</v>
+        <v>0.02444271798652567</v>
       </c>
       <c r="C3" t="n">
         <v>0.1018579889442992</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8103546067770725</v>
+        <v>0.8103546067770723</v>
       </c>
     </row>
     <row r="4">
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2756487250199113</v>
+        <v>0.2756487250199114</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2218639632557895</v>
+        <v>0.2218639632557894</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2140808095272581</v>
+        <v>0.2140808095272575</v>
       </c>
     </row>
     <row r="5">
@@ -1647,7 +1647,7 @@
         <v>0.1664421345423985</v>
       </c>
       <c r="D5" t="n">
-        <v>2.263476248329056e-06</v>
+        <v>2.263476248329077e-06</v>
       </c>
     </row>
     <row r="6">
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1791283976706456</v>
+        <v>-0.1791283976706459</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2049919256074302</v>
+        <v>0.2049919256074305</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3822100343131282</v>
+        <v>0.3822100343131284</v>
       </c>
     </row>
     <row r="7">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1904728809612527</v>
+        <v>0.1904728809612528</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1830828687785754</v>
+        <v>0.1830828687785755</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2981706802576984</v>
+        <v>0.298170680257699</v>
       </c>
     </row>
     <row r="8">
@@ -1689,13 +1689,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02585714966741434</v>
+        <v>0.0258571496674143</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1931377319540168</v>
+        <v>0.1931377319540171</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8934979973795407</v>
+        <v>0.8934979973795411</v>
       </c>
     </row>
     <row r="9">
@@ -1708,10 +1708,10 @@
         <v>1.078492441903574</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1625051351014593</v>
+        <v>0.1625051351014595</v>
       </c>
       <c r="D9" t="n">
-        <v>3.208557236656847e-11</v>
+        <v>3.208557236657033e-11</v>
       </c>
     </row>
     <row r="10">
@@ -1721,13 +1721,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1453095305392677</v>
+        <v>0.1453095305392678</v>
       </c>
       <c r="C10" t="n">
-        <v>0.266753036826706</v>
+        <v>0.2667530368267064</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5859362662578781</v>
+        <v>0.5859362662578784</v>
       </c>
     </row>
     <row r="11">
@@ -1740,10 +1740,10 @@
         <v>0.2258952284551363</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2567372932128584</v>
+        <v>0.2567372932128586</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3789301892340624</v>
+        <v>0.3789301892340627</v>
       </c>
     </row>
     <row r="12">
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2238722198593791</v>
+        <v>-0.2238722198593792</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2921431009265691</v>
+        <v>0.2921431009265689</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4434917877305512</v>
+        <v>0.4434917877305503</v>
       </c>
     </row>
     <row r="13">
@@ -1785,13 +1785,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2380082564065347</v>
+        <v>0.2380082564065346</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2619585733909518</v>
+        <v>0.2619585733909509</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3635760286774815</v>
+        <v>0.3635760286774802</v>
       </c>
     </row>
     <row r="15">
@@ -1804,10 +1804,10 @@
         <v>0.2909332948528223</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2546715666353525</v>
+        <v>0.2546715666353526</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2532935059734768</v>
+        <v>0.2532935059734769</v>
       </c>
     </row>
     <row r="16">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1481947915129312</v>
+        <v>0.1481947915129311</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2510856640294915</v>
+        <v>0.2510856640294903</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5550458059667087</v>
+        <v>0.5550458059667072</v>
       </c>
     </row>
     <row r="17">
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1147419350152481</v>
+        <v>0.114741935015248</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2634654661960734</v>
+        <v>0.2634654661960728</v>
       </c>
       <c r="D17" t="n">
-        <v>0.663192034600413</v>
+        <v>0.6631920346004125</v>
       </c>
     </row>
     <row r="18">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3810056013756247</v>
+        <v>0.3810056013756248</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2516542446197348</v>
+        <v>0.2516542446197337</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1300247560438152</v>
+        <v>0.1300247560438135</v>
       </c>
     </row>
     <row r="19">
@@ -1865,13 +1865,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07577207202969742</v>
+        <v>0.07577207202969728</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2639063601658794</v>
+        <v>0.2639063601658793</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7740225338446043</v>
+        <v>0.7740225338446046</v>
       </c>
     </row>
     <row r="20">
@@ -1887,7 +1887,7 @@
         <v>0.265725401909625</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5688274538815593</v>
+        <v>0.5688274538815595</v>
       </c>
     </row>
     <row r="21">
@@ -1900,10 +1900,10 @@
         <v>0.2002496868151333</v>
       </c>
       <c r="C21" t="n">
-        <v>0.25490381217693</v>
+        <v>0.2549038121769297</v>
       </c>
       <c r="D21" t="n">
-        <v>0.432108182350737</v>
+        <v>0.4321081823507363</v>
       </c>
     </row>
     <row r="22">
@@ -1913,13 +1913,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.02074852137919054</v>
+        <v>-0.02074852137919063</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2743224548273922</v>
+        <v>0.2743224548273923</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9397090769219666</v>
+        <v>0.9397090769219663</v>
       </c>
     </row>
     <row r="23">
@@ -1935,7 +1935,7 @@
         <v>0.2792240338270775</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6240617685694627</v>
+        <v>0.6240617685694625</v>
       </c>
     </row>
     <row r="24">
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8213945685289854</v>
+        <v>0.8213945685289853</v>
       </c>
       <c r="C24" t="n">
         <v>0.1484879382665879</v>
       </c>
       <c r="D24" t="n">
-        <v>3.170952111067024e-08</v>
+        <v>3.170952111067041e-08</v>
       </c>
     </row>
     <row r="25">
@@ -1961,13 +1961,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.6343958972733733</v>
+        <v>-0.6343958972733734</v>
       </c>
       <c r="C25" t="n">
         <v>0.1108031950759136</v>
       </c>
       <c r="D25" t="n">
-        <v>1.031722996890038e-08</v>
+        <v>1.031722996890046e-08</v>
       </c>
     </row>
     <row r="26">
@@ -1977,13 +1977,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1361722920117852</v>
+        <v>-0.1361722920117855</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1456889183422691</v>
+        <v>0.1456889183422689</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3499540372786675</v>
+        <v>0.3499540372786659</v>
       </c>
     </row>
     <row r="27">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.07214589570780619</v>
+        <v>-0.07214589570780622</v>
       </c>
       <c r="C27" t="n">
         <v>0.1495438291756702</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6294935505006782</v>
+        <v>0.6294935505006781</v>
       </c>
     </row>
     <row r="28">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.08070056949942785</v>
+        <v>-0.08070056949942789</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1455600496406539</v>
+        <v>0.1455600496406537</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5792953583346238</v>
+        <v>0.579295358334623</v>
       </c>
     </row>
     <row r="29">
@@ -2025,77 +2025,77 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2670893546719089</v>
+        <v>-0.267089354671909</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1498065967867206</v>
+        <v>0.1498065967867202</v>
       </c>
       <c r="D29" t="n">
-        <v>0.07460348161738017</v>
+        <v>0.07460348161737926</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.01036511117109708</v>
+        <v>0.00227667580555176</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007653933807267039</v>
+        <v>0.007061859833278293</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1756661613316849</v>
+        <v>0.7471569571762009</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01050692349724878</v>
+        <v>0.01407014842112886</v>
       </c>
       <c r="C31" t="n">
-        <v>0.006731266320498094</v>
+        <v>0.02184983277761062</v>
       </c>
       <c r="D31" t="n">
-        <v>0.118544195748189</v>
+        <v>0.5196093827488828</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01407014842112891</v>
+        <v>-0.01036511117109709</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02184983277761078</v>
+        <v>0.007653933807267214</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5196093827488846</v>
+        <v>0.175666161331694</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002276675805551766</v>
+        <v>0.01050692349724877</v>
       </c>
       <c r="C33" t="n">
-        <v>0.007061859833278298</v>
+        <v>0.006731266320498111</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7471569571762005</v>
+        <v>0.1185441957481902</v>
       </c>
     </row>
   </sheetData>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9203819593624207</v>
+        <v>0.9203819593624183</v>
       </c>
       <c r="D2" t="n">
         <v>0.8975852151944936</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0227967441679271</v>
+        <v>0.02279674416792465</v>
       </c>
     </row>
     <row r="3">
@@ -2168,13 +2168,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9076439572638432</v>
+        <v>0.9076439572638408</v>
       </c>
       <c r="D3" t="n">
         <v>0.8579106117563428</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04973334550750041</v>
+        <v>0.04973334550749808</v>
       </c>
     </row>
     <row r="4">
@@ -2187,13 +2187,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8958640717713853</v>
+        <v>0.8958640717713829</v>
       </c>
       <c r="D4" t="n">
         <v>0.8263333274535157</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06953074431786954</v>
+        <v>0.06953074431786721</v>
       </c>
     </row>
     <row r="5">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8710411710941867</v>
+        <v>0.8710411710941836</v>
       </c>
       <c r="D5" t="n">
         <v>0.794717184639996</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0763239864541907</v>
+        <v>0.07632398645418759</v>
       </c>
     </row>
   </sheetData>
@@ -2253,10 +2253,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.443505627120432</v>
+        <v>3.443505627120429</v>
       </c>
       <c r="B2" t="n">
-        <v>0.06350082160297774</v>
+        <v>0.06350082160297775</v>
       </c>
       <c r="C2" t="n">
         <v>3.977080931513962</v>
@@ -2265,217 +2265,217 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5903149678536211</v>
+        <v>0.5903149678536181</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4422973484463532</v>
+        <v>0.4422973484463544</v>
       </c>
       <c r="C3" t="n">
-        <v>1.176911501519807</v>
+        <v>1.176911501519803</v>
       </c>
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.6457416250634048</v>
+        <v>0.6457416250634053</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4216392867904263</v>
+        <v>0.4216392867904259</v>
       </c>
       <c r="C4" t="n">
-        <v>1.245918796657313</v>
+        <v>1.245918796657314</v>
       </c>
       <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.1158610022023816</v>
+        <v>0.115861002202381</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7335676596604714</v>
+        <v>0.7335676596604721</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4469980577481762</v>
+        <v>0.4469980577481749</v>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.1658506004757251</v>
+        <v>0.1658506004757244</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6838261508744673</v>
+        <v>0.6838261508744679</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5482984995282986</v>
+        <v>0.5482984995282973</v>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0555496857214403</v>
+        <v>0.05554968572144049</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8136733789568205</v>
+        <v>0.8136733789568202</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2974783042324353</v>
+        <v>0.2974783042324357</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.342656090985952</v>
+        <v>2.342656090985944</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1258747664385362</v>
+        <v>0.1258747664385375</v>
       </c>
       <c r="C8" t="n">
-        <v>2.989938993583034</v>
+        <v>2.989938993583019</v>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.4191648223707315</v>
+        <v>0.4191648223707344</v>
       </c>
       <c r="B9" t="n">
-        <v>0.517354076081846</v>
+        <v>0.5173540760818445</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9507760987492896</v>
+        <v>0.9507760987492939</v>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2.56308762080192</v>
+        <v>2.563087620801925</v>
       </c>
       <c r="B10" t="n">
-        <v>0.109384762054885</v>
+        <v>0.1093847620548851</v>
       </c>
       <c r="C10" t="n">
-        <v>3.192516318722249</v>
+        <v>3.192516318722248</v>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.01850173438861422</v>
+        <v>0.01850173438861394</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8918046158754545</v>
+        <v>0.8918046158754552</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1652004279969336</v>
+        <v>0.1652004279969323</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.7148191238207384</v>
+        <v>0.7148191238207335</v>
       </c>
       <c r="B12" t="n">
-        <v>0.397848606788927</v>
+        <v>0.3978486067889285</v>
       </c>
       <c r="C12" t="n">
-        <v>1.329708548003164</v>
+        <v>1.329708548003158</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.04867934936202147</v>
+        <v>0.04867934936202035</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8253774474283412</v>
+        <v>0.8253774474283433</v>
       </c>
       <c r="C13" t="n">
-        <v>0.276874076130251</v>
+        <v>0.2768740761302473</v>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.1821552994077157</v>
+        <v>0.182155299407713</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6695275158805057</v>
+        <v>0.6695275158805081</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5787847470172138</v>
+        <v>0.5787847470172088</v>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.2993532444747626</v>
+        <v>0.2993532444747617</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5842881627155665</v>
+        <v>0.5842881627155672</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7752480333376625</v>
+        <v>0.7752480333376608</v>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.04913171654298526</v>
+        <v>0.04913171654298504</v>
       </c>
       <c r="B16" t="n">
-        <v>0.82458109803095</v>
+        <v>0.8245810980309505</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2782667043496737</v>
+        <v>0.2782667043496729</v>
       </c>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.184202881563925</v>
+        <v>1.184202881563922</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2765020303717787</v>
+        <v>0.2765020303717791</v>
       </c>
       <c r="C17" t="n">
-        <v>1.85463802058817</v>
+        <v>1.854638020588168</v>
       </c>
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1.012957618056931</v>
+        <v>1.012957618056929</v>
       </c>
       <c r="B18" t="n">
-        <v>0.3141953264390928</v>
+        <v>0.3141953264390932</v>
       </c>
       <c r="C18" t="n">
-        <v>1.67026637375013</v>
+        <v>1.670266373750128</v>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2.804172748136175</v>
+        <v>2.804172748136147</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0940193292733911</v>
+        <v>0.09401932927339279</v>
       </c>
       <c r="C19" t="n">
-        <v>3.410898801280982</v>
+        <v>3.410898801280956</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.009052018172401151</v>
+        <v>0.009052018172401106</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9242019630174031</v>
+        <v>0.9242019630174032</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1137199410759848</v>
+        <v>0.1137199410759846</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
@@ -2493,7 +2493,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.3637986136795444</v>
+        <v>0.3637986136795445</v>
       </c>
       <c r="B22" t="n">
         <v>0.5464041140521181</v>
@@ -2505,133 +2505,133 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1.530686883471331</v>
+        <v>1.53068688347133</v>
       </c>
       <c r="B23" t="n">
-        <v>0.2160093850510954</v>
+        <v>0.2160093850510955</v>
       </c>
       <c r="C23" t="n">
-        <v>2.210834099755398</v>
+        <v>2.210834099755397</v>
       </c>
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.01620963059960664</v>
+        <v>0.01620963059960668</v>
       </c>
       <c r="B24" t="n">
-        <v>0.8986894681032693</v>
+        <v>0.8986894681032692</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1541053998591765</v>
+        <v>0.1541053998591767</v>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2.275397032810745</v>
+        <v>2.275397032810749</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1314414603749755</v>
+        <v>0.1314414603749735</v>
       </c>
       <c r="C25" t="n">
-        <v>2.927507680393381</v>
+        <v>2.927507680393403</v>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.0677059193606587</v>
+        <v>0.06770591936065652</v>
       </c>
       <c r="B26" t="n">
-        <v>0.7947067187302173</v>
+        <v>0.7947067187302206</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3315055533556245</v>
+        <v>0.3315055533556185</v>
       </c>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.1600402696707896</v>
+        <v>0.1600402696707893</v>
       </c>
       <c r="B27" t="n">
-        <v>0.6891194441918256</v>
+        <v>0.6891194441918258</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5371740297978385</v>
+        <v>0.537174029797838</v>
       </c>
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5.661975765712</v>
+        <v>5.661975765712011</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0173365827060886</v>
+        <v>0.01733658270608849</v>
       </c>
       <c r="C28" t="n">
-        <v>5.850036639475991</v>
+        <v>5.850036639476</v>
       </c>
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.5185416276853725</v>
+        <v>0.5185416276853763</v>
       </c>
       <c r="B29" t="n">
-        <v>0.4714644459190896</v>
+        <v>0.4714644459190879</v>
       </c>
       <c r="C29" t="n">
-        <v>1.084779116415929</v>
+        <v>1.084779116415934</v>
       </c>
       <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.6121910312997699</v>
+        <v>0.6121910312997706</v>
       </c>
       <c r="B30" t="n">
-        <v>0.4339640388345909</v>
+        <v>0.4339640388345904</v>
       </c>
       <c r="C30" t="n">
-        <v>1.204352598633608</v>
+        <v>1.20435259863361</v>
       </c>
       <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.4311172894155737</v>
+        <v>0.4311172894155775</v>
       </c>
       <c r="B31" t="n">
-        <v>0.5114412200502637</v>
+        <v>0.5114412200502618</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9673596543594232</v>
+        <v>0.9673596543594285</v>
       </c>
       <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.7749116540198883</v>
+        <v>0.7749116540198736</v>
       </c>
       <c r="B32" t="n">
-        <v>0.3787018686058168</v>
+        <v>0.3787018686058216</v>
       </c>
       <c r="C32" t="n">
-        <v>1.400865555044237</v>
+        <v>1.400865555044219</v>
       </c>
       <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2.228476646075275</v>
+        <v>2.228476646075272</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1354873718065581</v>
+        <v>0.1354873718065585</v>
       </c>
       <c r="C33" t="n">
-        <v>2.883769704423106</v>
+        <v>2.883769704423102</v>
       </c>
       <c r="D33" t="inlineStr"/>
     </row>
